--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-moped-ext-beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-moped-ext-beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:58:51+00:00</t>
+    <t>2024-11-06T10:59:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-moped-ext-beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-moped-ext-beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:59:22+00:00</t>
+    <t>2024-11-06T11:18:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
